--- a/stats for com eng/excel files/Ch4-03.xlsx
+++ b/stats for com eng/excel files/Ch4-03.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B5AE77-EA60-6841-AEB6-FC13B6205C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD72A44-AE4E-5F41-AD54-A99D340BC69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13160" activeTab="2" xr2:uid="{4C1FC052-56B3-4703-985E-36351D15350F}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11040" activeTab="5" xr2:uid="{4C1FC052-56B3-4703-985E-36351D15350F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet1 practice" sheetId="7" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2 practice" sheetId="8" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet3 practice" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="62">
   <si>
     <r>
       <t>Alpha (</t>
@@ -348,6 +351,90 @@
   <si>
     <t>TRYING TO FIND A TRUE POPULATION PROPORTION, FROM SAMPLE THAT WE HAVE</t>
   </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>s^2 is sample variance</t>
+  </si>
+  <si>
+    <t>(n-1)*s^2/X1-a, n-1</t>
+  </si>
+  <si>
+    <t>X is from the right</t>
+  </si>
+  <si>
+    <r>
+      <t>Chi-square (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) (alpha/2) critical value from right</t>
+    </r>
+  </si>
+  <si>
+    <t>chi square alpha/2 from the right</t>
+  </si>
+  <si>
+    <t>Confidennce interval</t>
+  </si>
+  <si>
+    <t>chi square 1-alpha/2 from the right</t>
+  </si>
+  <si>
+    <r>
+      <t>z(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Symbol"/>
+        <family val="1"/>
+        <charset val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/2) critical value</t>
+    </r>
+  </si>
+  <si>
+    <t>Confidence interval</t>
+  </si>
 </sst>
 </file>
 
@@ -356,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,8 +487,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,8 +526,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -493,11 +593,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -526,6 +637,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,6 +706,55 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>467831</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ED0F9B8-409D-BA40-A3F7-202312A4FAB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2044700" y="34925"/>
+          <a:ext cx="4417531" cy="1638300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -773,7 +935,188 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>124188</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>649</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416BEA6D-513F-C940-9F1D-36F61DC926F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3092449" y="361950"/>
+          <a:ext cx="4512039" cy="1353199"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>14381</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>100855</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>436910</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>145679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BF77295-098B-F840-834D-A71A767E377C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14381" y="2958355"/>
+          <a:ext cx="5210429" cy="1187824"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>420622</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>145561</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77CA0EA6-7D0D-3E4E-9B52-806D11D99728}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6105525"/>
+          <a:ext cx="5208522" cy="707536"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>17169</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>354868</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>184513</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB368AC-6706-C24C-85BC-6F91A578DC8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8260188"/>
+          <a:ext cx="5139333" cy="742438"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -811,6 +1154,55 @@
         <a:xfrm>
           <a:off x="5087175" y="516610"/>
           <a:ext cx="4525094" cy="1320578"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523785</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>129152</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>327636</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>93629</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9790C113-0048-1649-909B-BBA8577F7122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5083085" y="510152"/>
+          <a:ext cx="4515551" cy="1297977"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1407,6 +1799,312 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DD3647-100D-6449-AFF2-4F6942B72B5F}">
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="34.5" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="10">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="10">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="10">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="10">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="10">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10">
+        <v>177</v>
+      </c>
+      <c r="H10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10">
+        <v>175</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3">
+        <f>COUNT(B2:B22)</f>
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="10">
+        <v>171</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3">
+        <f>_xlfn.VAR.S(B2:B22)</f>
+        <v>48.257142857142853</v>
+      </c>
+      <c r="H12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="10">
+        <v>171</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10">
+        <v>168</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="10">
+        <v>164</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="10">
+        <v>163</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="3">
+        <f>E11-1</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="10">
+        <v>178</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="10">
+        <v>170</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="10">
+        <v>170</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="4">
+        <f>(E11-1)*E12/L20</f>
+        <v>24.130473927656681</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="10">
+        <v>168</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="4">
+        <f>(E11-1)*E12/L21</f>
+        <v>129.83092233383735</v>
+      </c>
+      <c r="I20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20">
+        <f>_xlfn.CHISQ.INV.RT(E14/2, E16)</f>
+        <v>39.996846312938644</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="10">
+        <v>180</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="4">
+        <f>SQRT(G19)</f>
+        <v>4.9122778756557208</v>
+      </c>
+      <c r="I21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21">
+        <f>_xlfn.CHISQ.INV.RT(1-E14/2, E16)</f>
+        <v>7.4338442629342358</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="10">
+        <v>170</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="4">
+        <f>SQRT(G20)</f>
+        <v>11.394337292437738</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB70879-FBF3-44CD-B728-62FD3C66D189}">
   <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1626,7 +2324,232 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B2554BD-1370-624F-AD98-7F5434FF72DB}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4">
+        <f>B4/B3</f>
+        <v>0.11764705882352941</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1">
+        <f>B7/2</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4">
+        <f>_xlfn.NORM.S.INV(1-B8)</f>
+        <v>1.9599639845400536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4">
+        <f>B5-B9*SQRT(B5*(1-B5)/B3)</f>
+        <v>4.9153405048878593E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <f>B5+B9*SQRT(B5*(1-B5)/B3)</f>
+        <v>0.18614071259818021</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14">
+        <f>_xlfn.NORM.S.INV(1-B7)</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="4">
+        <f>_xlfn.NORM.S.INV(1-B7)</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="4">
+        <f>B5-B14*SQRT(B5*(1-B5)/B3)</f>
+        <v>6.0165372566508092E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="6">
+        <f>B24</f>
+        <v>1.6448536269514715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="4">
+        <f>B5+B14*SQRT(B5*(1-B5)/B3)</f>
+        <v>0.17512874508055074</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="8">
+        <f>_xlfn.NORM.S.INV(1-B8)</f>
+        <v>1.9599639845400536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="7">
+        <f>0.05</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="8">
+        <f>B5</f>
+        <v>0.11764705882352941</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="3">
+        <f>(B39/B40)^2*B41*(1-B41)</f>
+        <v>159.50694065165911</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="3">
+        <v>160</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="3">
+        <f>(B39/B40)^2*0.25</f>
+        <v>384.14588206941232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="3">
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8682E1B4-2263-453D-83C1-91CD0A8547F2}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1881,4 +2804,264 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{712EBBB6-FD60-2441-8C0B-AAAEEA367814}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="10">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="10">
+        <v>166</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3">
+        <f>COUNT(B2:B22)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="10">
+        <v>180</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
+        <f>COUNTIF(B2:B22, "&gt;=170")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="10">
+        <v>185</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4">
+        <f>E4/E3</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="10">
+        <v>177</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="10">
+        <v>168</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="10">
+        <v>154</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <f>0.01/2</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="10">
+        <v>175</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4">
+        <f>_xlfn.NORM.S.INV(1-E8)</f>
+        <v>2.5758293035488999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="10">
+        <v>177</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10">
+        <v>175</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4">
+        <f>E5-E9*SQRT(E5*(1-E5)/E3)</f>
+        <v>0.40169393968792166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="10">
+        <v>171</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="17">
+        <f>E5+E9*SQRT(E5*(1-E5)/E3)</f>
+        <v>0.9316393936454116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="10">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10">
+        <v>168</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="10">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="10">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="10">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="10">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>